--- a/testplan.xlsx
+++ b/testplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SV\apb_protocol_UVM_tb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3C2FFF-6E98-420B-97BB-C39BDD3BF1DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD09E89-D1EC-4072-A540-EC77B4ED2976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
   <si>
     <t>Директория</t>
   </si>
@@ -143,6 +143,43 @@
 3) Подать: pready=1, prdata
 4) Подать несколько раз без опускания transfer
 5) Проверить: psel1, psel2, pwrite=1, paddr, pwdata, penable=1</t>
+  </si>
+  <si>
+    <t>В процессе</t>
+  </si>
+  <si>
+    <t>sequential_rw_test</t>
+  </si>
+  <si>
+    <t>Проверка случайных последовательных операций</t>
+  </si>
+  <si>
+    <t>1) Сброс
+2) Подать: transfer=1, случайную операцию с допустимыми адресами
+3) Подать несколько раз без опускания transfer
+4) Проверить: psel1, psel2, pwrite, paddr, pwdata, apb_read_data_out, penable=1</t>
+  </si>
+  <si>
+    <t>rw_with_wait_states_test</t>
+  </si>
+  <si>
+    <t>Проверка поддержки wait states</t>
+  </si>
+  <si>
+    <t>1) Сброс
+2) Начать операцию
+3) Удерживать pready=0 несколько тактов</t>
+  </si>
+  <si>
+    <t>pslverr_handling_test</t>
+  </si>
+  <si>
+    <t>Проверка реакции на сигнал ошибки от slave</t>
+  </si>
+  <si>
+    <t>1) Сброс
+2) Начать операцию
+3) Подать pslverr=1 вместе с pready=1</t>
   </si>
 </sst>
 </file>
@@ -653,7 +690,7 @@
         <v>22</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>13</v>
@@ -676,7 +713,7 @@
         <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -699,7 +736,7 @@
         <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>13</v>
@@ -722,7 +759,7 @@
         <v>23</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -797,32 +834,74 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
+    <row r="10" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
